--- a/daily_matches/job_matches_2026-08-08.xlsx
+++ b/daily_matches/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Senior Generative AI Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, CI/CD, Terraform, Git, Kafka, PostgreSQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Prompt Engineering, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Data Scientist (Applied AI)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Terraform, Kafka, Hadoop, NoSQL, Tableau, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, S3, Glue, MLflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9a9587bf83f262bf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Terraform, Kafka, Hadoop, NoSQL, Tableau, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Data Lake, CI/CD, Git</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Pinecone, Prompt Engineering, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e919c95fbd4b9d68</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, CI/CD, Jenkins, Terraform, Git, Databricks, Kafka, Python</t>
+          <t>AI Engineer, RAG, S3, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, S3, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java + Testing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, EC2, Docker, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, CI/CD, Terraform, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d385afe4a6f4c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Innovation Partner Senior</t>
+          <t>Data Analyst (Software Implementation)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The University of Kansas Health System</t>
+          <t>Collins Engineers, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shawnee Mission, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Synapse, Data Lake, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>RAG, Gemini, Copilot, BigQuery, Dataflow, Git, BigQuery, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc807996b3099050</t>
+          <t>https://www.indeed.com/viewjob?jk=f687932337d5b816</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer with GCP experience</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Oak Street Health, part of CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Python, SQL</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, Snowflake, BigQuery, PySpark, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acbbd59be258741d</t>
+          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>GCP Cloud Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Python, SQL</t>
+          <t>RAG, BigQuery, Dataflow, Kubernetes, Snowflake, Databricks, BigQuery, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,94 +811,94 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34427f88ecc67f28</t>
+          <t>https://www.indeed.com/viewjob?jk=c206f8689e93c0ab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, CI/CD, Terraform, Git, Snowflake, BigQuery</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Full Stack Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Canyon Bicycles USA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>Copilot, BigQuery, AKS, Git, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa4a41248eaa62a</t>
+          <t>https://www.indeed.com/viewjob?jk=df54e56582e8dc01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer - GenAI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, FastAPI, Docker, CI/CD, Git, Kafka, MongoDB, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
+          <t>https://www.indeed.com/viewjob?jk=3887a758ab12980a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salesforce Technical AI Engineer (Senior Consultant, Technical Transformation)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>RePurpose Global</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Databricks, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8024469f982bda98</t>
+          <t>https://www.indeed.com/viewjob?jk=9135b171c7ecd48b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>URBN Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>URBN</t>
+          <t>RePurpose Global</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Hugging Face, PyTorch, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e6d81f53581352</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e6c2a5a7b46eea</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>RePurpose Global</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b69bad8bf8dc05d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6702a6b7e6f3e3bf</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,172 +1056,172 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d1d36524adc8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=116af8b0fbe3531c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer (Java, APIs, AWS)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RePurpose Global</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c02701a46e2e149c</t>
+          <t>https://www.indeed.com/viewjob?jk=384dad83d169aff1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Role</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RePurpose Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Data Lake, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75c257944b4c3da</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff874bf61fa327c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RePurpose Global</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, Copilot, Docker, CI/CD, GitHub Actions, Git, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d18f832e997d63</t>
+          <t>https://www.indeed.com/viewjob?jk=7fef4f77841b2f9b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III (Python/AuthE)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RePurpose Global</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, MySQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d41f7a733acdd383</t>
+          <t>https://www.indeed.com/viewjob?jk=e927d0e06217a7a9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Holland LP</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>University Park, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, Redshift, Hadoop, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699679b067b06197</t>
+          <t>https://www.indeed.com/viewjob?jk=0f472942144e5def</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applied AI/ML Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>intangible</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, TensorFlow, PyTorch, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91826d578e11df45</t>
+          <t>https://www.indeed.com/viewjob?jk=82cf389533c3cd5d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Finance Data Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Amerita</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=759b1f399fe0e472</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer - Core Platform &amp; Embedded Reliability (Hybrid)</t>
+          <t>Senior Data Scientist – Generative AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Git, Kafka, Cassandra, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Snowflake, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae8bdacbe9ff967</t>
+          <t>https://www.indeed.com/viewjob?jk=746526c1d53f9bcf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Machine Learning Engineer Role</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=0c0ae38e5e53c965</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Geospatial Solution Analyst - Machine Learning</t>
+          <t>Full-Stack AI Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAM Companies</t>
+          <t>H.W. Kaufman Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Terraform, SQL, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8297bcfaff1e9af</t>
+          <t>https://www.indeed.com/viewjob?jk=12c508bbe8619db9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Experienced QA Engineer with Hands-on Automation and AI Skills</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, NLTK, CI/CD, Jenkins, Git, Python, R</t>
+          <t>RAG, Docker, Jenkins, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6844f5a70b8a0eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=2694269f315de74f</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184450a069faf372</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c834a451db623</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=006663fa97661cab</t>
+          <t>https://www.indeed.com/viewjob?jk=533d8c434315d268</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1936b762ee420c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0061a1981c0ac850</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c4c2d3f47ae0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=12c1607e16c617a0</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b626cb0891c0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=a5df8ba82f9eb635</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8d90f5126b81302</t>
+          <t>https://www.indeed.com/viewjob?jk=8d3e3426421e9cf9</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d075d4195e2251a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f28e623ee16fc79</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db9ac05b79bdc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3834106f5d18506</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90da0a934ecc8d46</t>
+          <t>https://www.indeed.com/viewjob?jk=bbfd2923552465bc</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667dae01d47222db</t>
+          <t>https://www.indeed.com/viewjob?jk=0d99eeb81a827d6b</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec33bd4927f4941</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c21820f966604b</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ea65014aa4eb40</t>
+          <t>https://www.indeed.com/viewjob?jk=666bda2d7d20c2a7</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22489360edcfc450</t>
+          <t>https://www.indeed.com/viewjob?jk=9e5619b261f15122</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785d370f8512b3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=505c20bf82f1dbcf</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d5483c994abaea</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fbc3a3eade56c6</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f890f7d16bd433b7</t>
+          <t>https://www.indeed.com/viewjob?jk=108745e672ce2a3a</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a2f9e13c0e73d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f1edb2c0b4786346</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301d32d5be8f6d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ade3fa693d0fdf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Experienced QA Engineer with Hands-on Automation and AI Skills</t>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, NLTK, CI/CD, Jenkins, Git, Python, R</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed89f6b14eed5dd</t>
+          <t>https://www.indeed.com/viewjob?jk=523a633fe6abcd2f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer — Healthcare AI</t>
+          <t>2027 Technology, Data, AI &amp; Ventures Summer Internship Program - AI Engineer (MLOps) Intern</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef72f2fb8275b718</t>
+          <t>https://www.indeed.com/viewjob?jk=70a6d46ffd48b44c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, SQL, R, Java, Optimization</t>
+          <t>RAG, Git, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58ade195556d51</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Embedded Software Engineer - Physical AI</t>
+          <t>2027 Data for Good Hackathon - Data &amp; AI Program - Summer Internship</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, CI/CD, Git, Python, R, Optimization</t>
+          <t>RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ed83d67a86609e</t>
+          <t>https://www.indeed.com/viewjob?jk=5007812dace4d224</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>US - Analytics Engineer</t>
+          <t>Senior HR Data Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shriners Children's</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Data Scientist, Synapse, CI/CD, Databricks, PySpark, Power BI, SQL, R, Scala</t>
+          <t>RAG, Snowflake, Databricks, MySQL, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d69350e97d4bec</t>
+          <t>https://www.indeed.com/viewjob?jk=a42955ea5a889d6b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Analyst, Applications Engineering &amp; Manufacturing</t>
+          <t>Senior Software Engineer Cloud Microservices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Anderson Merchandisers</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Snowflake, MySQL, Tableau, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,182 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea78f20e14aa50</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Data Scientist - Biostatistics &amp; Data Science</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>University of Kansas Medical Center</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, MySQL, Tableau, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7b554f5f2419d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>AI and Agentic Engineer I</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Exelixis</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Alameda, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d384fd773c2846c</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>AI and Agentic Engineer II</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Exelixis</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Alameda, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, Databricks, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8202d965a2b749a</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>UNITED STATES SOCCER FEDERATION 1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Git, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=697b1a6b2458300f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3b5d6d623c0cbf0</t>
         </is>
       </c>
     </row>
